--- a/XLS/SCRAPE_single_video.xlsx
+++ b/XLS/SCRAPE_single_video.xlsx
@@ -425,30 +425,32 @@
         <v>publish_date</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Só quem é filho da fé vai entender 🙏  
+#filhodafe #Samuelbatistafilho #Deus #</v>
       </c>
       <c r="B2">
-        <v>205600</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+        <v>1700000</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Só quem é filho da fé vai entender 🙏  
+#filhodafe #Samuelbatistafilho #Deus #estrada #gospel </v>
       </c>
       <c r="D2">
-        <v>2961</v>
+        <v>130400</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>filhodafe, samuelbatistafilho, deus, estrada, gospel</v>
       </c>
       <c r="F2" t="str">
-        <v>https://www.tiktok.com/@789534ra/video/7608357297735191829</v>
+        <v>https://www.tiktok.com/@samuelbatistaofc0/video/7620446586878823698</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>1351</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-02-18T23:52:24.000Z</v>
+        <v>2026-03-23T13:44:51.000Z</v>
       </c>
     </row>
   </sheetData>
